--- a/Experiment_1/results/Experiment_1_results.xlsx
+++ b/Experiment_1/results/Experiment_1_results.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="34">
   <si>
     <t>Phoenix Train</t>
   </si>
@@ -73,13 +73,19 @@
     <t>Diff MicroScan Test</t>
   </si>
   <si>
+    <t>ROC</t>
+  </si>
+  <si>
+    <t>F1 Score</t>
+  </si>
+  <si>
     <t>Phoenix Baseline</t>
   </si>
   <si>
-    <t>ROC</t>
-  </si>
-  <si>
-    <t>F1 Score</t>
+    <t>ME</t>
+  </si>
+  <si>
+    <t>VME</t>
   </si>
   <si>
     <t>Sample count</t>
@@ -89,13 +95,31 @@
   </si>
   <si>
     <t>Train R</t>
+  </si>
+  <si>
+    <t>Phoenix count</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>VITEK count</t>
+  </si>
+  <si>
+    <t>MicroScan count</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -121,6 +145,11 @@
       <name val="Arial"/>
     </font>
     <font/>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica Neue"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -198,7 +227,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -220,13 +249,7 @@
     <xf borderId="1" fillId="0" fontId="3" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="top"/>
     </xf>
     <xf borderId="2" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -234,7 +257,20 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="2" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" vertical="top"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1327,6 +1363,21 @@
       <c r="F26" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="I26" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="L26" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="M26" s="7" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="27">
       <c r="B27" s="4" t="s">
@@ -1344,6 +1395,13 @@
       <c r="F27" s="6">
         <v>0.793776895067858</v>
       </c>
+      <c r="I27" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
+      <c r="M27" s="10"/>
     </row>
     <row r="28">
       <c r="B28" s="4" t="s">
@@ -1361,6 +1419,21 @@
       <c r="F28" s="6">
         <v>0.822960372960372</v>
       </c>
+      <c r="I28" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="J28" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="K28" s="6">
+        <v>0.921348314606741</v>
+      </c>
+      <c r="L28" s="6">
+        <v>0.812658227848101</v>
+      </c>
+      <c r="M28" s="6">
+        <v>0.793776895067858</v>
+      </c>
     </row>
     <row r="29">
       <c r="B29" s="4" t="s">
@@ -1378,6 +1451,21 @@
       <c r="F29" s="6">
         <v>0.658447488584474</v>
       </c>
+      <c r="I29" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J29" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="K29" s="6">
+        <v>0.935483870967741</v>
+      </c>
+      <c r="L29" s="6">
+        <v>0.8634375</v>
+      </c>
+      <c r="M29" s="6">
+        <v>0.822960372960372</v>
+      </c>
     </row>
     <row r="30">
       <c r="B30" s="4" t="s">
@@ -1395,11 +1483,33 @@
       <c r="F30" s="6">
         <v>0.862404543324235</v>
       </c>
+      <c r="I30" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J30" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="K30" s="6">
+        <v>0.894009216589861</v>
+      </c>
+      <c r="L30" s="6">
+        <v>0.92764817150063</v>
+      </c>
+      <c r="M30" s="6">
+        <v>0.862404543324235</v>
+      </c>
     </row>
     <row r="31">
       <c r="B31" s="3" t="s">
         <v>2</v>
       </c>
+      <c r="I31" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="J31" s="9"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="9"/>
+      <c r="M31" s="10"/>
     </row>
     <row r="32">
       <c r="B32" s="2" t="s">
@@ -1417,6 +1527,21 @@
       <c r="F32" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="I32" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="J32" s="6">
+        <v>0.991031390134529</v>
+      </c>
+      <c r="K32" s="6">
+        <v>0.915730337078651</v>
+      </c>
+      <c r="L32" s="6">
+        <v>0.783287837427964</v>
+      </c>
+      <c r="M32" s="6">
+        <v>0.784033001698616</v>
+      </c>
     </row>
     <row r="33">
       <c r="B33" s="4" t="s">
@@ -1434,6 +1559,21 @@
       <c r="F33" s="6">
         <v>0.784033001698616</v>
       </c>
+      <c r="I33" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J33" s="6">
+        <v>0.969581749049429</v>
+      </c>
+      <c r="K33" s="6">
+        <v>0.930875576036866</v>
+      </c>
+      <c r="L33" s="6">
+        <v>0.860516934046345</v>
+      </c>
+      <c r="M33" s="6">
+        <v>0.827458256029684</v>
+      </c>
     </row>
     <row r="34">
       <c r="B34" s="4" t="s">
@@ -1451,6 +1591,21 @@
       <c r="F34" s="6">
         <v>0.827458256029684</v>
       </c>
+      <c r="I34" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J34" s="6">
+        <v>0.680608365019011</v>
+      </c>
+      <c r="K34" s="6">
+        <v>0.585253456221198</v>
+      </c>
+      <c r="L34" s="6">
+        <v>0.756771799628942</v>
+      </c>
+      <c r="M34" s="6">
+        <v>0.579674586776859</v>
+      </c>
     </row>
     <row r="35">
       <c r="B35" s="4" t="s">
@@ -1468,6 +1623,13 @@
       <c r="F35" s="6">
         <v>0.643662868051136</v>
       </c>
+      <c r="I35" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J35" s="9"/>
+      <c r="K35" s="9"/>
+      <c r="L35" s="9"/>
+      <c r="M35" s="10"/>
     </row>
     <row r="36">
       <c r="B36" s="4" t="s">
@@ -1485,11 +1647,41 @@
       <c r="F36" s="6">
         <v>0.579674586776859</v>
       </c>
+      <c r="I36" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="J36" s="6">
+        <v>0.96788990825688</v>
+      </c>
+      <c r="K36" s="6">
+        <v>0.932584269662921</v>
+      </c>
+      <c r="L36" s="6">
+        <v>0.800520833333333</v>
+      </c>
+      <c r="M36" s="6">
+        <v>0.814583333333333</v>
+      </c>
     </row>
     <row r="37">
       <c r="B37" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="I37" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J37" s="6">
+        <v>0.963133640552995</v>
+      </c>
+      <c r="K37" s="6">
+        <v>0.944700460829493</v>
+      </c>
+      <c r="L37" s="6">
+        <v>0.874269005847953</v>
+      </c>
+      <c r="M37" s="6">
+        <v>0.826953748006379</v>
+      </c>
     </row>
     <row r="38">
       <c r="B38" s="2" t="s">
@@ -1507,6 +1699,21 @@
       <c r="F38" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="I38" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J38" s="6">
+        <v>0.930875576036866</v>
+      </c>
+      <c r="K38" s="6">
+        <v>0.870967741935483</v>
+      </c>
+      <c r="L38" s="6">
+        <v>0.892016317016317</v>
+      </c>
+      <c r="M38" s="6">
+        <v>0.822960372960372</v>
+      </c>
     </row>
     <row r="39">
       <c r="B39" s="4" t="s">
@@ -1577,83 +1784,72 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="7"/>
-      <c r="B46" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="7"/>
-      <c r="G46" s="9" t="s">
+      <c r="A46" s="12"/>
+      <c r="B46" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C46" s="12"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="J46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H46" s="9" t="s">
+      <c r="K46" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="I46" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="J46" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="K46" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L46" s="7"/>
-      <c r="M46" s="7"/>
-      <c r="N46" s="7"/>
-      <c r="O46" s="7"/>
-      <c r="P46" s="7"/>
-      <c r="Q46" s="7"/>
-      <c r="R46" s="7"/>
-      <c r="S46" s="7"/>
-      <c r="T46" s="7"/>
-      <c r="U46" s="7"/>
-      <c r="V46" s="7"/>
-      <c r="W46" s="7"/>
-      <c r="X46" s="7"/>
-      <c r="Y46" s="7"/>
-      <c r="Z46" s="7"/>
-      <c r="AA46" s="7"/>
-      <c r="AB46" s="7"/>
+      <c r="L46" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M46" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="S46" s="12"/>
+      <c r="T46" s="12"/>
+      <c r="U46" s="12"/>
+      <c r="V46" s="12"/>
+      <c r="W46" s="12"/>
+      <c r="X46" s="12"/>
+      <c r="Y46" s="12"/>
+      <c r="Z46" s="12"/>
+      <c r="AA46" s="12"/>
+      <c r="AB46" s="12"/>
     </row>
     <row r="47">
       <c r="B47" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C47" s="9" t="s">
+      <c r="C47" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D47" s="9" t="s">
+      <c r="D47" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E47" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E47" s="9" t="s">
+      <c r="F47" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J47" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F47" s="7"/>
-      <c r="G47" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H47" s="11"/>
-      <c r="I47" s="11"/>
-      <c r="J47" s="11"/>
-      <c r="K47" s="12"/>
-      <c r="N47" s="7"/>
-      <c r="O47" s="7"/>
-      <c r="P47" s="7"/>
-      <c r="Q47" s="7"/>
-      <c r="R47" s="7"/>
-      <c r="S47" s="7"/>
-      <c r="T47" s="7"/>
-      <c r="U47" s="7"/>
-      <c r="V47" s="7"/>
-      <c r="W47" s="7"/>
-      <c r="X47" s="7"/>
-      <c r="Y47" s="7"/>
-      <c r="Z47" s="7"/>
-      <c r="AA47" s="7"/>
-      <c r="AB47" s="7"/>
+      <c r="K47" s="9"/>
+      <c r="L47" s="9"/>
+      <c r="M47" s="9"/>
+      <c r="S47" s="12"/>
+      <c r="T47" s="12"/>
+      <c r="U47" s="12"/>
+      <c r="V47" s="12"/>
+      <c r="W47" s="12"/>
+      <c r="X47" s="12"/>
+      <c r="Y47" s="12"/>
+      <c r="Z47" s="12"/>
+      <c r="AA47" s="12"/>
+      <c r="AB47" s="12"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="B48" s="4" t="s">
@@ -1668,37 +1864,34 @@
       <c r="E48" s="6">
         <v>0.793776895067858</v>
       </c>
-      <c r="F48" s="7"/>
-      <c r="G48" s="13" t="s">
+      <c r="F48" s="14">
+        <v>3.37078651685393</v>
+      </c>
+      <c r="G48" s="14">
+        <v>4.49438202247191</v>
+      </c>
+      <c r="J48" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H48" s="6">
+      <c r="K48" s="6">
         <v>1.0</v>
       </c>
-      <c r="I48" s="6">
-        <v>0.921348314606741</v>
-      </c>
-      <c r="J48" s="6">
-        <v>0.812658227848101</v>
-      </c>
-      <c r="K48" s="6">
-        <v>0.793776895067858</v>
-      </c>
-      <c r="N48" s="7"/>
-      <c r="O48" s="7"/>
-      <c r="P48" s="7"/>
-      <c r="Q48" s="7"/>
-      <c r="R48" s="7"/>
-      <c r="S48" s="7"/>
-      <c r="T48" s="7"/>
-      <c r="U48" s="7"/>
-      <c r="V48" s="7"/>
-      <c r="W48" s="7"/>
-      <c r="X48" s="7"/>
-      <c r="Y48" s="7"/>
-      <c r="Z48" s="7"/>
-      <c r="AA48" s="7"/>
-      <c r="AB48" s="7"/>
+      <c r="L48" s="14">
+        <v>3.37078651685393</v>
+      </c>
+      <c r="M48" s="14">
+        <v>4.49438202247191</v>
+      </c>
+      <c r="S48" s="12"/>
+      <c r="T48" s="12"/>
+      <c r="U48" s="12"/>
+      <c r="V48" s="12"/>
+      <c r="W48" s="12"/>
+      <c r="X48" s="12"/>
+      <c r="Y48" s="12"/>
+      <c r="Z48" s="12"/>
+      <c r="AA48" s="12"/>
+      <c r="AB48" s="12"/>
     </row>
     <row r="49">
       <c r="B49" s="4" t="s">
@@ -1713,40 +1906,37 @@
       <c r="E49" s="6">
         <v>0.822960372960372</v>
       </c>
-      <c r="F49" s="7"/>
-      <c r="G49" s="13" t="s">
+      <c r="F49" s="14">
+        <v>1.84331797235023</v>
+      </c>
+      <c r="G49" s="14">
+        <v>4.60829493087557</v>
+      </c>
+      <c r="J49" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="H49" s="6">
+      <c r="K49" s="6">
         <v>1.0</v>
       </c>
-      <c r="I49" s="6">
-        <v>0.935483870967741</v>
-      </c>
-      <c r="J49" s="6">
-        <v>0.8634375</v>
-      </c>
-      <c r="K49" s="6">
-        <v>0.822960372960372</v>
-      </c>
-      <c r="N49" s="7"/>
-      <c r="O49" s="7"/>
-      <c r="P49" s="7"/>
-      <c r="Q49" s="7"/>
-      <c r="R49" s="7"/>
-      <c r="S49" s="7"/>
-      <c r="T49" s="7"/>
-      <c r="U49" s="7"/>
-      <c r="V49" s="7"/>
-      <c r="W49" s="7"/>
-      <c r="X49" s="7"/>
-      <c r="Y49" s="7"/>
-      <c r="Z49" s="7"/>
-      <c r="AA49" s="7"/>
-      <c r="AB49" s="7"/>
+      <c r="L49" s="14">
+        <v>1.84331797235023</v>
+      </c>
+      <c r="M49" s="14">
+        <v>4.60829493087557</v>
+      </c>
+      <c r="S49" s="12"/>
+      <c r="T49" s="12"/>
+      <c r="U49" s="12"/>
+      <c r="V49" s="12"/>
+      <c r="W49" s="12"/>
+      <c r="X49" s="12"/>
+      <c r="Y49" s="12"/>
+      <c r="Z49" s="12"/>
+      <c r="AA49" s="12"/>
+      <c r="AB49" s="12"/>
     </row>
     <row r="50">
-      <c r="A50" s="7"/>
+      <c r="A50" s="12"/>
       <c r="B50" s="4" t="s">
         <v>18</v>
       </c>
@@ -1759,78 +1949,76 @@
       <c r="E50" s="6">
         <v>0.862404543324235</v>
       </c>
-      <c r="F50" s="7"/>
-      <c r="G50" s="13" t="s">
+      <c r="F50" s="14">
+        <v>3.2258064516129</v>
+      </c>
+      <c r="G50" s="14">
+        <v>7.37327188940092</v>
+      </c>
+      <c r="J50" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H50" s="6">
+      <c r="K50" s="6">
         <v>1.0</v>
       </c>
-      <c r="I50" s="6">
-        <v>0.894009216589861</v>
-      </c>
-      <c r="J50" s="6">
-        <v>0.92764817150063</v>
-      </c>
-      <c r="K50" s="6">
-        <v>0.862404543324235</v>
-      </c>
-      <c r="M50" s="7"/>
-      <c r="N50" s="7"/>
-      <c r="O50" s="7"/>
-      <c r="P50" s="7"/>
-      <c r="Q50" s="7"/>
-      <c r="R50" s="7"/>
-      <c r="S50" s="7"/>
-      <c r="T50" s="7"/>
-      <c r="U50" s="7"/>
-      <c r="V50" s="7"/>
-      <c r="W50" s="7"/>
-      <c r="X50" s="7"/>
-      <c r="Y50" s="7"/>
-      <c r="Z50" s="7"/>
-      <c r="AA50" s="7"/>
-      <c r="AB50" s="7"/>
+      <c r="L50" s="14">
+        <v>3.2258064516129</v>
+      </c>
+      <c r="M50" s="14">
+        <v>7.37327188940092</v>
+      </c>
+      <c r="S50" s="12"/>
+      <c r="T50" s="12"/>
+      <c r="U50" s="12"/>
+      <c r="V50" s="12"/>
+      <c r="W50" s="12"/>
+      <c r="X50" s="12"/>
+      <c r="Y50" s="12"/>
+      <c r="Z50" s="12"/>
+      <c r="AA50" s="12"/>
+      <c r="AB50" s="12"/>
     </row>
     <row r="51">
       <c r="B51" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G51" s="10" t="s">
+      <c r="J51" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="H51" s="11"/>
-      <c r="I51" s="11"/>
-      <c r="J51" s="11"/>
-      <c r="K51" s="12"/>
+      <c r="K51" s="9"/>
+      <c r="L51" s="9"/>
+      <c r="M51" s="9"/>
     </row>
     <row r="52">
       <c r="B52" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C52" s="9" t="s">
+      <c r="C52" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D52" s="9" t="s">
+      <c r="D52" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E52" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E52" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="G52" s="13" t="s">
+      <c r="F52" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J52" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H52" s="6">
+      <c r="K52" s="6">
         <v>0.991031390134529</v>
       </c>
-      <c r="I52" s="6">
-        <v>0.915730337078651</v>
-      </c>
-      <c r="J52" s="6">
-        <v>0.783287837427964</v>
-      </c>
-      <c r="K52" s="6">
-        <v>0.784033001698616</v>
+      <c r="L52" s="14">
+        <v>3.37078651685393</v>
+      </c>
+      <c r="M52" s="14">
+        <v>5.05617977528089</v>
       </c>
     </row>
     <row r="53">
@@ -1846,20 +2034,23 @@
       <c r="E53" s="6">
         <v>0.784033001698616</v>
       </c>
-      <c r="G53" s="13" t="s">
+      <c r="F53" s="14">
+        <v>3.37078651685393</v>
+      </c>
+      <c r="G53" s="14">
+        <v>5.05617977528089</v>
+      </c>
+      <c r="J53" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="H53" s="6">
+      <c r="K53" s="6">
         <v>0.969581749049429</v>
       </c>
-      <c r="I53" s="6">
-        <v>0.930875576036866</v>
-      </c>
-      <c r="J53" s="6">
-        <v>0.860516934046345</v>
-      </c>
-      <c r="K53" s="6">
-        <v>0.827458256029684</v>
+      <c r="L53" s="14">
+        <v>0.921658986175115</v>
+      </c>
+      <c r="M53" s="14">
+        <v>5.99078341013824</v>
       </c>
     </row>
     <row r="54">
@@ -1875,20 +2066,23 @@
       <c r="E54" s="6">
         <v>0.827458256029684</v>
       </c>
-      <c r="G54" s="13" t="s">
+      <c r="F54" s="14">
+        <v>0.921658986175115</v>
+      </c>
+      <c r="G54" s="14">
+        <v>5.99078341013824</v>
+      </c>
+      <c r="J54" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H54" s="6">
+      <c r="K54" s="6">
         <v>0.680608365019011</v>
       </c>
-      <c r="I54" s="6">
-        <v>0.585253456221198</v>
-      </c>
-      <c r="J54" s="6">
-        <v>0.756771799628942</v>
-      </c>
-      <c r="K54" s="6">
-        <v>0.579674586776859</v>
+      <c r="L54" s="14">
+        <v>0.460829493087557</v>
+      </c>
+      <c r="M54" s="14">
+        <v>41.0138248847926</v>
       </c>
     </row>
     <row r="55">
@@ -1904,61 +2098,68 @@
       <c r="E55" s="6">
         <v>0.579674586776859</v>
       </c>
-      <c r="G55" s="10" t="s">
+      <c r="F55" s="14">
+        <v>0.460829493087557</v>
+      </c>
+      <c r="G55" s="14">
+        <v>41.0138248847926</v>
+      </c>
+      <c r="J55" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="H55" s="11"/>
-      <c r="I55" s="11"/>
-      <c r="J55" s="11"/>
-      <c r="K55" s="12"/>
+      <c r="K55" s="9"/>
+      <c r="L55" s="9"/>
+      <c r="M55" s="9"/>
     </row>
     <row r="56">
       <c r="B56" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G56" s="13" t="s">
+      <c r="F56" s="15"/>
+      <c r="G56" s="15"/>
+      <c r="J56" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H56" s="6">
+      <c r="K56" s="6">
         <v>0.96788990825688</v>
       </c>
-      <c r="I56" s="6">
-        <v>0.932584269662921</v>
-      </c>
-      <c r="J56" s="6">
-        <v>0.800520833333333</v>
-      </c>
-      <c r="K56" s="6">
-        <v>0.814583333333333</v>
+      <c r="L56" s="14">
+        <v>3.37078651685393</v>
+      </c>
+      <c r="M56" s="14">
+        <v>3.37078651685393</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C57" s="9" t="s">
+      <c r="C57" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D57" s="9" t="s">
+      <c r="D57" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E57" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E57" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="G57" s="13" t="s">
+      <c r="F57" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="G57" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="J57" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="H57" s="6">
+      <c r="K57" s="6">
         <v>0.963133640552995</v>
       </c>
-      <c r="I57" s="6">
-        <v>0.944700460829493</v>
-      </c>
-      <c r="J57" s="6">
-        <v>0.874269005847953</v>
-      </c>
-      <c r="K57" s="6">
-        <v>0.826953748006379</v>
+      <c r="L57" s="14">
+        <v>2.76497695852534</v>
+      </c>
+      <c r="M57" s="14">
+        <v>2.76497695852534</v>
       </c>
     </row>
     <row r="58">
@@ -1974,20 +2175,23 @@
       <c r="E58" s="6">
         <v>0.814583333333333</v>
       </c>
-      <c r="G58" s="13" t="s">
+      <c r="F58" s="14">
+        <v>3.37078651685393</v>
+      </c>
+      <c r="G58" s="14">
+        <v>3.37078651685393</v>
+      </c>
+      <c r="J58" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H58" s="6">
+      <c r="K58" s="6">
         <v>0.930875576036866</v>
       </c>
-      <c r="I58" s="6">
-        <v>0.870967741935483</v>
-      </c>
-      <c r="J58" s="6">
-        <v>0.892016317016317</v>
-      </c>
-      <c r="K58" s="6">
-        <v>0.822960372960372</v>
+      <c r="L58" s="14">
+        <v>6.4516129032258</v>
+      </c>
+      <c r="M58" s="14">
+        <v>6.4516129032258</v>
       </c>
     </row>
     <row r="59">
@@ -2003,6 +2207,12 @@
       <c r="E59" s="6">
         <v>0.826953748006379</v>
       </c>
+      <c r="F59" s="14">
+        <v>2.76497695852534</v>
+      </c>
+      <c r="G59" s="14">
+        <v>2.76497695852534</v>
+      </c>
     </row>
     <row r="60">
       <c r="B60" s="4" t="s">
@@ -2017,38 +2227,44 @@
       <c r="E60" s="6">
         <v>0.822960372960372</v>
       </c>
+      <c r="F60" s="14">
+        <v>6.4516129032258</v>
+      </c>
+      <c r="G60" s="14">
+        <v>6.4516129032258</v>
+      </c>
     </row>
     <row r="63">
       <c r="B63" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C64" s="14">
+      <c r="C64" s="17">
         <v>178.0</v>
       </c>
       <c r="D64" s="6">
         <v>0.98</v>
       </c>
-      <c r="E64" s="14">
+      <c r="E64" s="17">
         <v>68.0</v>
       </c>
-      <c r="F64" s="14">
+      <c r="F64" s="17">
         <v>384.0</v>
       </c>
     </row>
@@ -2056,16 +2272,16 @@
       <c r="B65" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C65" s="14">
+      <c r="C65" s="17">
         <v>217.0</v>
       </c>
       <c r="D65" s="6">
         <v>0.94</v>
       </c>
-      <c r="E65" s="14">
+      <c r="E65" s="17">
         <v>54.0</v>
       </c>
-      <c r="F65" s="14">
+      <c r="F65" s="17">
         <v>398.0</v>
       </c>
     </row>
@@ -2073,35 +2289,188 @@
       <c r="B66" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C66" s="14">
+      <c r="C66" s="17">
         <v>217.0</v>
       </c>
       <c r="D66" s="6">
         <v>0.58</v>
       </c>
-      <c r="E66" s="14">
+      <c r="E66" s="17">
         <v>164.0</v>
       </c>
-      <c r="F66" s="14">
+      <c r="F66" s="17">
         <v>288.0</v>
       </c>
     </row>
+    <row r="69">
+      <c r="K69" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L69" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M69" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N69" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="K70" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="L70" s="5">
+        <v>20.0</v>
+      </c>
+      <c r="M70" s="5">
+        <v>158.0</v>
+      </c>
+      <c r="N70" s="5">
+        <v>178.0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="K71" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="L71" s="5">
+        <v>25.0</v>
+      </c>
+      <c r="M71" s="5">
+        <v>192.0</v>
+      </c>
+      <c r="N71" s="5">
+        <v>217.0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="K72" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="L72" s="5">
+        <v>61.0</v>
+      </c>
+      <c r="M72" s="5">
+        <v>156.0</v>
+      </c>
+      <c r="N72" s="5">
+        <v>217.0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="K73" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="K74" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="L74" s="5">
+        <v>21.0</v>
+      </c>
+      <c r="M74" s="5">
+        <v>157.0</v>
+      </c>
+      <c r="N74" s="5">
+        <v>178.0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="K75" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="L75" s="5">
+        <v>30.0</v>
+      </c>
+      <c r="M75" s="5">
+        <v>187.0</v>
+      </c>
+      <c r="N75" s="5">
+        <v>217.0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="K76" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="L76" s="5">
+        <v>140.0</v>
+      </c>
+      <c r="M76" s="5">
+        <v>77.0</v>
+      </c>
+      <c r="N76" s="5">
+        <v>217.0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="K77" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="K78" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="L78" s="5">
+        <v>18.0</v>
+      </c>
+      <c r="M78" s="5">
+        <v>160.0</v>
+      </c>
+      <c r="N78" s="5">
+        <v>178.0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="K79" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="L79" s="5">
+        <v>19.0</v>
+      </c>
+      <c r="M79" s="5">
+        <v>198.0</v>
+      </c>
+      <c r="N79" s="5">
+        <v>217.0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="K80" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="L80" s="5">
+        <v>52.0</v>
+      </c>
+      <c r="M80" s="5">
+        <v>165.0</v>
+      </c>
+      <c r="N80" s="5">
+        <v>217.0</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="10">
+    <mergeCell ref="I35:M35"/>
+    <mergeCell ref="I31:M31"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="E1:I1"/>
     <mergeCell ref="J1:N1"/>
     <mergeCell ref="O1:S1"/>
-    <mergeCell ref="G47:K47"/>
-    <mergeCell ref="G51:K51"/>
-    <mergeCell ref="G55:K55"/>
+    <mergeCell ref="I27:M27"/>
+    <mergeCell ref="J47:M47"/>
+    <mergeCell ref="J51:M51"/>
+    <mergeCell ref="J55:M55"/>
   </mergeCells>
-  <conditionalFormatting sqref="V4:V7 C9:F12 U9 V10:V13 C15:F18 C21:F24 C27:F30 C33:F36 C39:F44 F47:F50 C48:E50 H48:K50 F52:F55 H52:K54 C53:E55 H56:H58 I56:K60 C58:F60 D64:D66">
+  <conditionalFormatting sqref="V4:V7 C9:F12 U9 V10:V13 C15:F18 C21:F24 C27:F30 J28:M30 J32:M34 C33:F36 J36:M38 C39:F44 C48:E50 K48:K50 K52:K54 C53:E55 K56:K60 C58:E60 I59:J60 D64:D66">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>0.95</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V4:V7 C9:F12 U9 V10:V13 C15:F18 C21:F24 C27:F30 C33:F36 C39:F44 F47:F50 C48:E50 H48:K50 F52:F55 H52:K54 C53:E55 H56:H58 I56:K60 C58:F60 D64:D66">
+  <conditionalFormatting sqref="V4:V7 C9:F12 U9 V10:V13 C15:F18 C21:F24 C27:F30 J28:M30 J32:M34 C33:F36 J36:M38 C39:F44 C48:E50 K48:K50 K52:K54 C53:E55 K56:K60 C58:E60 I59:J60 D64:D66">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
       <formula>0.85</formula>
     </cfRule>
